--- a/Excel/sales_dashboard.xlsx
+++ b/Excel/sales_dashboard.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kiran Kumar\sales-analysis-project\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93BCF307-1F7E-44CC-94C4-ECC74CEF6985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABCB05C-08F1-4BBC-81D8-960706167009}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="994" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,9 +29,9 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="11" r:id="rId9"/>
-    <pivotCache cacheId="6" r:id="rId10"/>
-    <pivotCache cacheId="10" r:id="rId11"/>
+    <pivotCache cacheId="0" r:id="rId9"/>
+    <pivotCache cacheId="1" r:id="rId10"/>
+    <pivotCache cacheId="2" r:id="rId11"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="41">
   <si>
     <t>total_revenue</t>
   </si>
@@ -129,9 +129,6 @@
   </si>
   <si>
     <t>Grand Total</t>
-  </si>
-  <si>
-    <t>2024</t>
   </si>
   <si>
     <t>Sum of TOTAL_REVENUE</t>
@@ -249,6 +246,9 @@
       </rPr>
       <t xml:space="preserve"> </t>
     </r>
+  </si>
+  <si>
+    <t>2022</t>
   </si>
 </sst>
 </file>
@@ -413,31 +413,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="5">
+    <dxf>
+      <numFmt numFmtId="164" formatCode="[$€-2]\ #,##0"/>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -465,27 +486,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="[$€-2]\ #,##0"/>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
       </border>
     </dxf>
   </dxfs>
@@ -799,7 +799,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Office</c:v>
+                  <c:v>Clothing</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -811,7 +811,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>3139724.29</c:v>
+                  <c:v>2945353.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1404,7 +1404,7 @@
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>2024</c:v>
+                    <c:v>2022</c:v>
                   </c:pt>
                 </c:lvl>
               </c:multiLvlStrCache>
@@ -1417,40 +1417,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="12"/>
                 <c:pt idx="0">
-                  <c:v>414543.73</c:v>
+                  <c:v>424619.87</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>393369.8</c:v>
+                  <c:v>374257.3</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>449463.44</c:v>
+                  <c:v>425126.01</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>455790.15</c:v>
+                  <c:v>394769.94</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>471889.43</c:v>
+                  <c:v>380524.77</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>439426.11</c:v>
+                  <c:v>397044.08</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>425390.97</c:v>
+                  <c:v>421121.94</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>431551.19</c:v>
+                  <c:v>425276.35</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>435790.96</c:v>
+                  <c:v>444301.17</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>406923.22</c:v>
+                  <c:v>404436.62</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>461174.65</c:v>
+                  <c:v>414188.9</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>441955.07</c:v>
+                  <c:v>397426.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1984,41 +1984,23 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:strRef>
-              <c:f>PIVOT_Region_Revenue!$A$4:$A$8</c:f>
+              <c:f>PIVOT_Region_Revenue!$A$4:$A$5</c:f>
               <c:strCache>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>East</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>North</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>South</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>West</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>PIVOT_Region_Revenue!$B$4:$B$8</c:f>
+              <c:f>PIVOT_Region_Revenue!$B$4:$B$5</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="4"/>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
                   <c:v>3873231.43</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>3752970.69</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>3796181.84</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>3871728.04</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3987,8 +3969,8 @@
       <xdr:row>16</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="11" name="YEAR">
@@ -4011,7 +3993,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4060,13 +4042,13 @@
       <xdr:rowOff>15240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>624840</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1262030</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>144780</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="12" name="category">
@@ -4089,7 +4071,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4139,12 +4121,12 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>586740</xdr:colOff>
+      <xdr:colOff>586739</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="13" name="region">
@@ -4167,7 +4149,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4640,14 +4622,14 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3507A9CA-8E45-4500-8F42-33FE85C8F1F4}" name="PivotTable1" cacheId="11" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3507A9CA-8E45-4500-8F42-33FE85C8F1F4}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="14">
   <location ref="A3:B17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="6">
     <pivotField showAll="0">
       <items count="4">
-        <item h="1" x="0"/>
+        <item x="0"/>
         <item h="1" x="1"/>
-        <item x="2"/>
+        <item h="1" x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -4730,7 +4712,7 @@
   </rowFields>
   <rowItems count="14">
     <i>
-      <x v="3"/>
+      <x v="1"/>
     </i>
     <i r="1">
       <x v="1"/>
@@ -4811,15 +4793,15 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{40F353E6-A7FD-411A-8C3B-E46BCFBDE91B}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{40F353E6-A7FD-411A-8C3B-E46BCFBDE91B}" name="PivotTable1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0">
       <items count="6">
-        <item h="1" x="3"/>
+        <item x="3"/>
         <item h="1" x="4"/>
         <item h="1" x="1"/>
-        <item x="2"/>
+        <item h="1" x="2"/>
         <item h="1" x="0"/>
         <item t="default"/>
       </items>
@@ -4831,7 +4813,7 @@
   </rowFields>
   <rowItems count="2">
     <i>
-      <x v="3"/>
+      <x/>
     </i>
     <i t="grand">
       <x/>
@@ -4876,15 +4858,15 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{096361CA-870C-4897-8265-39C3593B542F}" name="PivotTable3" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{096361CA-870C-4897-8265-39C3593B542F}" name="PivotTable3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
+        <item h="1" x="3"/>
+        <item h="1" x="2"/>
+        <item h="1" x="1"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -4893,18 +4875,9 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="5">
+  <rowItems count="2">
     <i>
       <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -4947,9 +4920,9 @@
   <data>
     <tabular pivotCacheId="2123807219">
       <items count="3">
-        <i x="0"/>
+        <i x="0" s="1"/>
         <i x="1"/>
-        <i x="2" s="1"/>
+        <i x="2"/>
       </items>
     </tabular>
   </data>
@@ -4964,10 +4937,10 @@
   <data>
     <tabular pivotCacheId="1089026698">
       <items count="5">
-        <i x="3"/>
+        <i x="3" s="1"/>
         <i x="4"/>
         <i x="1"/>
-        <i x="2" s="1"/>
+        <i x="2"/>
         <i x="0"/>
       </items>
     </tabular>
@@ -4984,9 +4957,9 @@
     <tabular pivotCacheId="215654248">
       <items count="4">
         <i x="0" s="1"/>
-        <i x="3" s="1"/>
-        <i x="2" s="1"/>
-        <i x="1" s="1"/>
+        <i x="3"/>
+        <i x="2"/>
+        <i x="1"/>
       </items>
     </tabular>
   </data>
@@ -5002,13 +4975,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AAD83220-B46D-433C-9EA9-3DD603CFFD1E}" name="Table2" displayName="Table2" ref="H44:K49" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="3" tableBorderDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{AAD83220-B46D-433C-9EA9-3DD603CFFD1E}" name="Table2" displayName="Table2" ref="H44:K49" totalsRowShown="0" headerRowDxfId="4" headerRowBorderDxfId="3" tableBorderDxfId="2">
   <autoFilter ref="H44:K49" xr:uid="{AAD83220-B46D-433C-9EA9-3DD603CFFD1E}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{65B15882-73E7-4CFE-975D-1F91EFB849CB}" name="product_name"/>
     <tableColumn id="2" xr3:uid="{413A21AA-DB6D-4A45-9233-9029FABFE85F}" name="category"/>
-    <tableColumn id="3" xr3:uid="{769FAEBE-15E4-480C-8296-CC506F244785}" name="total_orders" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{FFD8E1C2-B2D6-4205-94A6-79DDFF4794FC}" name="total_revenue" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{769FAEBE-15E4-480C-8296-CC506F244785}" name="total_orders" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{FFD8E1C2-B2D6-4205-94A6-79DDFF4794FC}" name="total_revenue" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5285,49 +5258,49 @@
     <col min="3" max="3" width="32.109375" customWidth="1"/>
     <col min="6" max="6" width="1.6640625" customWidth="1"/>
     <col min="7" max="7" width="6.33203125" customWidth="1"/>
-    <col min="8" max="8" width="23.77734375" customWidth="1"/>
-    <col min="9" max="9" width="14.33203125" customWidth="1"/>
-    <col min="10" max="10" width="13.109375" customWidth="1"/>
-    <col min="11" max="11" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="26.88671875" customWidth="1"/>
+    <col min="9" max="9" width="21.5546875" customWidth="1"/>
+    <col min="10" max="10" width="19" customWidth="1"/>
+    <col min="11" max="11" width="22.44140625" customWidth="1"/>
     <col min="12" max="12" width="13.77734375" customWidth="1"/>
     <col min="13" max="13" width="12.77734375" customWidth="1"/>
     <col min="14" max="14" width="15.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:25" ht="44.4" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="16" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
-      <c r="V2" s="16"/>
-      <c r="W2" s="16"/>
-      <c r="X2" s="16"/>
-      <c r="Y2" s="16"/>
+      <c r="A2" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
+      <c r="N2" s="17"/>
+      <c r="O2" s="17"/>
+      <c r="P2" s="17"/>
+      <c r="Q2" s="17"/>
+      <c r="R2" s="17"/>
+      <c r="S2" s="17"/>
+      <c r="T2" s="17"/>
+      <c r="U2" s="17"/>
+      <c r="V2" s="17"/>
+      <c r="W2" s="17"/>
+      <c r="X2" s="17"/>
+      <c r="Y2" s="17"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="C3" s="15"/>
+      <c r="C3" s="16"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
-      <c r="C4" s="15"/>
+      <c r="C4" s="16"/>
     </row>
     <row r="11" spans="1:25" ht="35.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="18" spans="2:17" ht="21" x14ac:dyDescent="0.4">
@@ -5337,38 +5310,38 @@
     </row>
     <row r="19" spans="2:17" ht="33.6" x14ac:dyDescent="0.65">
       <c r="B19" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="18">
+        <v>39</v>
+      </c>
+      <c r="C19" s="14">
         <v>15294112</v>
       </c>
-      <c r="I19" s="14" t="s">
-        <v>38</v>
+      <c r="I19" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="J19" s="7"/>
       <c r="Q19" s="7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="43" spans="8:11" ht="18" x14ac:dyDescent="0.35">
-      <c r="H43" s="11" t="s">
+      <c r="H43" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I43" s="11"/>
-      <c r="J43" s="11"/>
-      <c r="K43" s="11"/>
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+      <c r="K43" s="15"/>
     </row>
     <row r="44" spans="8:11" x14ac:dyDescent="0.3">
-      <c r="H44" s="17" t="s">
+      <c r="H44" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="I44" s="17" t="s">
+      <c r="I44" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="J44" s="17" t="s">
+      <c r="J44" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="K44" s="17" t="s">
+      <c r="K44" s="13" t="s">
         <v>0</v>
       </c>
     </row>
@@ -5382,7 +5355,7 @@
       <c r="J45" s="9">
         <v>5197</v>
       </c>
-      <c r="K45" s="13">
+      <c r="K45" s="11">
         <v>3942935.32</v>
       </c>
     </row>
@@ -5396,7 +5369,7 @@
       <c r="J46" s="9">
         <v>4082</v>
       </c>
-      <c r="K46" s="13">
+      <c r="K46" s="11">
         <v>3161785.13</v>
       </c>
     </row>
@@ -5410,7 +5383,7 @@
       <c r="J47" s="9">
         <v>4080</v>
       </c>
-      <c r="K47" s="13">
+      <c r="K47" s="11">
         <v>3139724.29</v>
       </c>
     </row>
@@ -5424,7 +5397,7 @@
       <c r="J48" s="9">
         <v>3862</v>
       </c>
-      <c r="K48" s="13">
+      <c r="K48" s="11">
         <v>2945353.3</v>
       </c>
     </row>
@@ -5438,7 +5411,7 @@
       <c r="J49" s="9">
         <v>2779</v>
       </c>
-      <c r="K49" s="13">
+      <c r="K49" s="11">
         <v>2104313.96</v>
       </c>
     </row>
@@ -5477,119 +5450,119 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="12">
-        <v>5227268.7200000007</v>
+        <v>40</v>
+      </c>
+      <c r="B4" s="18">
+        <v>4903093.05</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="12">
-        <v>414543.73</v>
+        <v>23</v>
+      </c>
+      <c r="B5" s="18">
+        <v>424619.87</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="12">
-        <v>393369.8</v>
+        <v>24</v>
+      </c>
+      <c r="B6" s="18">
+        <v>374257.3</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="12">
-        <v>449463.44</v>
+        <v>25</v>
+      </c>
+      <c r="B7" s="18">
+        <v>425126.01</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="B8" s="12">
-        <v>455790.15</v>
+        <v>26</v>
+      </c>
+      <c r="B8" s="18">
+        <v>394769.94</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="12">
-        <v>471889.43</v>
+        <v>27</v>
+      </c>
+      <c r="B9" s="18">
+        <v>380524.77</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="B10" s="12">
-        <v>439426.11</v>
+        <v>28</v>
+      </c>
+      <c r="B10" s="18">
+        <v>397044.08</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="12">
-        <v>425390.97</v>
+        <v>29</v>
+      </c>
+      <c r="B11" s="18">
+        <v>421121.94</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="12">
-        <v>431551.19</v>
+        <v>30</v>
+      </c>
+      <c r="B12" s="18">
+        <v>425276.35</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B13" s="12">
-        <v>435790.96</v>
+        <v>31</v>
+      </c>
+      <c r="B13" s="18">
+        <v>444301.17</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="B14" s="12">
-        <v>406923.22</v>
+        <v>32</v>
+      </c>
+      <c r="B14" s="18">
+        <v>404436.62</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="12">
-        <v>461174.65</v>
+        <v>33</v>
+      </c>
+      <c r="B15" s="18">
+        <v>414188.9</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="12">
-        <v>441955.07</v>
+        <v>34</v>
+      </c>
+      <c r="B16" s="18">
+        <v>397426.1</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B17" s="12">
-        <v>5227268.7200000007</v>
+      <c r="B17" s="18">
+        <v>4903093.05</v>
       </c>
     </row>
   </sheetData>
@@ -6188,23 +6161,23 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="12">
-        <v>3139724.29</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="18">
+        <v>2945353.3</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B5" s="12">
-        <v>3139724.29</v>
+      <c r="B5" s="18">
+        <v>2945353.3</v>
       </c>
     </row>
   </sheetData>
@@ -6275,7 +6248,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1667FA24-05D7-45D6-BC5F-9BDC3A02781C}">
-  <dimension ref="A3:B8"/>
+  <dimension ref="A3:B5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
@@ -6287,47 +6260,23 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="18">
         <v>3873231.43</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="12">
-        <v>3752970.69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="12">
-        <v>3796181.84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7" s="12">
-        <v>3871728.04</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="12">
-        <v>15294112</v>
+      <c r="B5" s="18">
+        <v>3873231.43</v>
       </c>
     </row>
   </sheetData>
